--- a/data/Basic Functions and Conditional formatting task.xlsx
+++ b/data/Basic Functions and Conditional formatting task.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Assignments\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE444FB5-94CE-4275-9264-B044EE264720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="25">
   <si>
     <t>Yearly Sales Report</t>
   </si>
@@ -113,7 +114,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -201,7 +202,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -463,6 +464,17 @@
       <bottom style="medium">
         <color theme="9" tint="0.39997558519241921"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -470,7 +482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -498,6 +510,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -510,30 +541,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -544,6 +564,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{744D7A1C-696A-4C0A-B7BD-94CDB9063E48}" name="Table2" displayName="Table2" ref="J25:L28" totalsRowShown="0">
+  <autoFilter ref="J25:L28" xr:uid="{744D7A1C-696A-4C0A-B7BD-94CDB9063E48}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{812C87AC-9A73-4AE4-B11D-CFFE1C847A32}" name="Year"/>
+    <tableColumn id="2" xr3:uid="{2F47957E-5573-4F39-BE15-F0820A00063F}" name="Quantity" dataDxfId="1">
+      <calculatedColumnFormula>SUMIF($C$3:$C$26,Table2[[#This Row],[Year]],$E$3:$E$26)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{941265E8-9921-42C0-93E9-715A0F2FF501}" name="Amount" dataDxfId="0">
+      <calculatedColumnFormula>SUMIF($C$3:$C$26,Table2[[#This Row],[Year]],$F$3:$F$26)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -842,25 +878,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.453125" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="25" x14ac:dyDescent="0.5">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:21" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-    </row>
-    <row r="2" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+    </row>
+    <row r="2" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -880,7 +921,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -901,11 +942,11 @@
         <v>16720</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="35"/>
-      <c r="K3" s="36"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="30"/>
       <c r="N3" s="7"/>
       <c r="O3" s="8" t="s">
         <v>9</v>
@@ -914,7 +955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -953,9 +994,12 @@
       <c r="O4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="14"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P4" s="14">
+        <f>COUNTIF(D$3:D$26,$O4)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -978,16 +1022,28 @@
       <c r="H5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
+      <c r="I5" s="25">
+        <f>SUMIFS($F$3:$F$26,$C$3:$C$26,I$4,$D$3:$D$26,$H5)</f>
+        <v>12320</v>
+      </c>
+      <c r="J5" s="25">
+        <f>SUMIFS($F$3:$F$26,$C$3:$C$26,J$4,$D$3:$D$26,$H5)</f>
+        <v>23100</v>
+      </c>
+      <c r="K5" s="25">
+        <f>SUMIFS($F$3:$F$26,$C$3:$C$26,K$4,$D$3:$D$26,$H5)</f>
+        <v>25520</v>
+      </c>
       <c r="N5" s="32"/>
       <c r="O5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="14"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P5" s="14">
+        <f t="shared" ref="P5:P8" si="1">COUNTIF(D$3:D$26,$O5)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1010,16 +1066,28 @@
       <c r="H6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
+      <c r="I6" s="25">
+        <f>SUMIFS($F$3:$F$26,$C$3:$C$26,I$4,$D$3:$D$26,$H6)</f>
+        <v>16720</v>
+      </c>
+      <c r="J6" s="25">
+        <f t="shared" ref="I6:K9" si="2">SUMIFS($F$3:$F$26,$C$3:$C$26,J$4,$D$3:$D$26,$H6)</f>
+        <v>6160</v>
+      </c>
+      <c r="K6" s="25">
+        <f t="shared" si="2"/>
+        <v>7920</v>
+      </c>
       <c r="N6" s="32"/>
       <c r="O6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="14"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P6" s="14">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1042,16 +1110,28 @@
       <c r="H7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
+      <c r="I7" s="25">
+        <f>SUMIFS($F$3:$F$26,$C$3:$C$26,I$4,$D$3:$D$26,$H7)</f>
+        <v>26840</v>
+      </c>
+      <c r="J7" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="25">
+        <f>SUMIFS($F$3:$F$26,$C$3:$C$26,K$4,$D$3:$D$26,$H7)</f>
+        <v>15840</v>
+      </c>
       <c r="N7" s="32"/>
       <c r="O7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="P7" s="14"/>
-    </row>
-    <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P7" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1074,16 +1154,28 @@
       <c r="H8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
+      <c r="I8" s="25">
+        <f>SUMIFS($F$3:$F$26,$C$3:$C$26,I$4,$D$3:$D$26,$H8)</f>
+        <v>19800</v>
+      </c>
+      <c r="J8" s="25">
+        <f t="shared" si="2"/>
+        <v>20900</v>
+      </c>
+      <c r="K8" s="25">
+        <f t="shared" si="2"/>
+        <v>11440</v>
+      </c>
       <c r="N8" s="33"/>
       <c r="O8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="P8" s="14"/>
-    </row>
-    <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="14">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1106,11 +1198,20 @@
       <c r="H9" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="I9" s="25">
+        <f t="shared" si="2"/>
+        <v>29040</v>
+      </c>
+      <c r="J9" s="25">
+        <f>SUMIFS($F$3:$F$26,$C$3:$C$26,J$4,$D$3:$D$26,$H9)</f>
+        <v>33440</v>
+      </c>
+      <c r="K9" s="25">
+        <f t="shared" si="2"/>
+        <v>20240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1131,7 +1232,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1152,7 +1253,7 @@
         <v>7260</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1173,7 +1274,7 @@
         <v>20900</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1194,7 +1295,7 @@
         <v>12540</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1214,13 +1315,13 @@
       <c r="F14" s="4">
         <v>10560</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="30"/>
-    </row>
-    <row r="15" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I14" s="36"/>
+      <c r="J14" s="37"/>
+    </row>
+    <row r="15" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1257,13 +1358,13 @@
       <c r="O15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S15" s="34" t="s">
+      <c r="S15" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="T15" s="35"/>
-      <c r="U15" s="36"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="T15" s="29"/>
+      <c r="U15" s="30"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1286,16 +1387,28 @@
       <c r="H16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="16"/>
+      <c r="I16" s="13">
+        <f>SUM(E3:E26)</f>
+        <v>1224</v>
+      </c>
+      <c r="J16" s="16">
+        <f>SUM(F3:F26)</f>
+        <v>269280</v>
+      </c>
       <c r="L16" s="31" t="s">
         <v>23</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
+      <c r="N16" s="13">
+        <f>SUMIF($D$3:$D$26,$M16,$E$3:$E$26)</f>
+        <v>277</v>
+      </c>
+      <c r="O16" s="13">
+        <f>SUMIF($D$3:$D$26,$M16,$F$3:$F$26)</f>
+        <v>60940</v>
+      </c>
       <c r="R16" s="20" t="s">
         <v>4</v>
       </c>
@@ -1309,7 +1422,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1332,22 +1445,43 @@
       <c r="H17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="13"/>
-      <c r="J17" s="16"/>
+      <c r="I17" s="13">
+        <f>MIN(E3:E26)</f>
+        <v>24</v>
+      </c>
+      <c r="J17" s="16">
+        <f>MIN(F3:F26)</f>
+        <v>5280</v>
+      </c>
       <c r="L17" s="32"/>
       <c r="M17" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
+      <c r="N17" s="13">
+        <f t="shared" ref="N17:N20" si="3">SUMIF($D$3:$D$26,$M17,$E$3:$E$26)</f>
+        <v>140</v>
+      </c>
+      <c r="O17" s="13">
+        <f t="shared" ref="O17:O20" si="4">SUMIF($D$3:$D$26,$M17,$F$3:$F$26)</f>
+        <v>30800</v>
+      </c>
       <c r="R17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="S17" s="25">
+        <f>SUMIFS($E$3:$E$26,$C$3:$C$26,S$16,$D$3:$D$26,$R17)</f>
+        <v>56</v>
+      </c>
+      <c r="T17" s="25">
+        <f t="shared" ref="T17:U21" si="5">SUMIFS($E$3:$E$26,$C$3:$C$26,T$16,$D$3:$D$26,$R17)</f>
+        <v>105</v>
+      </c>
+      <c r="U17" s="25">
+        <f t="shared" si="5"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1370,22 +1504,43 @@
       <c r="H18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="16"/>
+      <c r="I18" s="13">
+        <f>MAX(E3:E26)</f>
+        <v>95</v>
+      </c>
+      <c r="J18" s="16">
+        <f>MAX(F3:F26)</f>
+        <v>20900</v>
+      </c>
       <c r="L18" s="32"/>
       <c r="M18" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="N18" s="13">
+        <f t="shared" si="3"/>
+        <v>194</v>
+      </c>
+      <c r="O18" s="13">
+        <f t="shared" si="4"/>
+        <v>42680</v>
+      </c>
       <c r="R18" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="S18" s="25">
+        <f t="shared" ref="S18:S21" si="6">SUMIFS($E$3:$E$26,$C$3:$C$26,S$16,$D$3:$D$26,$R18)</f>
+        <v>76</v>
+      </c>
+      <c r="T18" s="25">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="U18" s="25">
+        <f t="shared" si="5"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1408,22 +1563,43 @@
       <c r="H19" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="16"/>
+      <c r="I19" s="13">
+        <f>AVERAGE(E3:E26)</f>
+        <v>51</v>
+      </c>
+      <c r="J19" s="16">
+        <f>AVERAGE(F3:F26)</f>
+        <v>11220</v>
+      </c>
       <c r="L19" s="32"/>
       <c r="M19" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
+      <c r="N19" s="13">
+        <f t="shared" si="3"/>
+        <v>237</v>
+      </c>
+      <c r="O19" s="13">
+        <f t="shared" si="4"/>
+        <v>52140</v>
+      </c>
       <c r="R19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
-    </row>
-    <row r="20" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S19" s="25">
+        <f t="shared" si="6"/>
+        <v>122</v>
+      </c>
+      <c r="T19" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="25">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1446,22 +1622,43 @@
       <c r="H20" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="14"/>
+      <c r="I20" s="13">
+        <f>COUNT(E3:E26)</f>
+        <v>24</v>
+      </c>
+      <c r="J20" s="14">
+        <f>COUNT(F3:F26)</f>
+        <v>24</v>
+      </c>
       <c r="L20" s="33"/>
       <c r="M20" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
+      <c r="N20" s="13">
+        <f t="shared" si="3"/>
+        <v>376</v>
+      </c>
+      <c r="O20" s="13">
+        <f t="shared" si="4"/>
+        <v>82720</v>
+      </c>
       <c r="R20" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="S20" s="25"/>
-      <c r="T20" s="25"/>
-      <c r="U20" s="25"/>
-    </row>
-    <row r="21" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S20" s="25">
+        <f t="shared" si="6"/>
+        <v>90</v>
+      </c>
+      <c r="T20" s="25">
+        <f t="shared" si="5"/>
+        <v>95</v>
+      </c>
+      <c r="U20" s="25">
+        <f t="shared" si="5"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1484,16 +1681,39 @@
       <c r="H21" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="I21" s="13"/>
-      <c r="J21" s="19"/>
+      <c r="I21" s="13">
+        <f>COUNTA(E3:E26)</f>
+        <v>24</v>
+      </c>
+      <c r="J21" s="19">
+        <f>COUNTA(F3:F26)</f>
+        <v>24</v>
+      </c>
+      <c r="N21" s="27">
+        <f>SUM(N16:N20)</f>
+        <v>1224</v>
+      </c>
+      <c r="O21" s="27">
+        <f>SUM(O16:O20)</f>
+        <v>269280</v>
+      </c>
       <c r="R21" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="S21" s="25">
+        <f t="shared" si="6"/>
+        <v>132</v>
+      </c>
+      <c r="T21" s="25">
+        <f t="shared" si="5"/>
+        <v>152</v>
+      </c>
+      <c r="U21" s="25">
+        <f t="shared" si="5"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1514,7 +1734,7 @@
         <v>10340</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -1535,7 +1755,7 @@
         <v>9020</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -1556,7 +1776,7 @@
         <v>11440</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -1576,8 +1796,17 @@
       <c r="F25" s="4">
         <v>7920</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="J25" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -1597,16 +1826,56 @@
       <c r="F26" s="4">
         <v>13200</v>
       </c>
+      <c r="J26">
+        <v>2010</v>
+      </c>
+      <c r="K26">
+        <f>SUMIF($C$3:$C$26,Table2[[#This Row],[Year]],$E$3:$E$26)</f>
+        <v>476</v>
+      </c>
+      <c r="L26">
+        <f>SUMIF($C$3:$C$26,Table2[[#This Row],[Year]],$F$3:$F$26)</f>
+        <v>104720</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="J27">
+        <v>2011</v>
+      </c>
+      <c r="K27">
+        <f>SUMIF($C$3:$C$26,Table2[[#This Row],[Year]],$E$3:$E$26)</f>
+        <v>380</v>
+      </c>
+      <c r="L27">
+        <f>SUMIF($C$3:$C$26,Table2[[#This Row],[Year]],$F$3:$F$26)</f>
+        <v>83600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="J28">
+        <v>2012</v>
+      </c>
+      <c r="K28">
+        <f>SUMIF($C$3:$C$26,Table2[[#This Row],[Year]],$E$3:$E$26)</f>
+        <v>368</v>
+      </c>
+      <c r="L28">
+        <f>SUMIF($C$3:$C$26,Table2[[#This Row],[Year]],$F$3:$F$26)</f>
+        <v>80960</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="S15:U15"/>
+    <mergeCell ref="L16:L20"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="N4:N8"/>
-    <mergeCell ref="S15:U15"/>
-    <mergeCell ref="L16:L20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>